--- a/Result/profitability/1471.xlsx
+++ b/Result/profitability/1471.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.63</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07999999999999999</v>
+        <v>-0.08499999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>4.86125</v>
+        <v>1.81875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,16 +780,16 @@
         <v>-0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.12625</v>
+        <v>-0.07375</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4175</v>
+        <v>0.1275000000000003</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.58</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.02374999999999999</v>
+        <v>-0.0325</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1575</v>
+        <v>0.5125000000000003</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.71</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.26875</v>
+        <v>-0.21375</v>
       </c>
       <c r="N5" t="n">
-        <v>2.1375</v>
+        <v>-2.05125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.215</v>
+        <v>-0.1875</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1425</v>
+        <v>-2.205</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.21125</v>
+        <v>-0.2</v>
       </c>
       <c r="N7" t="n">
-        <v>1.03875</v>
+        <v>-1.97125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.74</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.13</v>
+        <v>-0.10375</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25875</v>
+        <v>1.49875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.04499999999999998</v>
       </c>
       <c r="N12" t="n">
-        <v>4.536250000000001</v>
+        <v>4.53625</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>25</v>
+      </c>
+      <c r="D75" t="n">
+        <v>30</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-18.33</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-33</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-130.62%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>60</v>
+      </c>
+      <c r="J75" t="n">
+        <v>27</v>
+      </c>
+      <c r="K75" t="n">
+        <v>27</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.02125000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1.95375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.920000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09481481481481491</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.692307692307692</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-33.51</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-2.207509881422925</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
